--- a/excel/case-assignment-fairness_dashboard.xlsx
+++ b/excel/case-assignment-fairness_dashboard.xlsx
@@ -288,6 +288,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_by_case_type'!$A$2:$A$7</f>
@@ -312,6 +313,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -340,6 +342,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -448,6 +451,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_by_case_type_3'!$A$2:$A$7</f>
@@ -476,6 +480,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_by_case_type_3'!$A$2:$A$7</f>
@@ -500,6 +505,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -513,6 +519,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -565,6 +572,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_routing'!$A$2:$A$4</f>
@@ -593,6 +601,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_routing'!$A$2:$A$4</f>
@@ -621,6 +630,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_routing'!$A$2:$A$4</f>
@@ -645,6 +655,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -658,6 +669,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -787,6 +799,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_reassign_cost'!$A$2:$A$5</f>
@@ -811,6 +824,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -838,6 +852,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <valAx>
         <axId val="200"/>
@@ -917,6 +932,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_complexity'!$A$2:$A$5</f>
@@ -945,6 +961,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_complexity'!$A$2:$A$5</f>
@@ -969,6 +986,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -982,6 +1000,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -1034,6 +1053,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_backlog'!$A$2:$A$6</f>
@@ -1058,6 +1078,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -1086,6 +1107,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -1134,6 +1156,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_root_cause'!$A$2:$A$9</f>
@@ -1158,6 +1181,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -1186,6 +1210,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
